--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="125">
   <si>
     <t>Mat</t>
   </si>
@@ -82,7 +82,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARIZMENDI</t>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -91,88 +124,103 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>NUÑEZ</t>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
   </si>
   <si>
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>MARROQUIN</t>
@@ -181,10 +229,31 @@
     <t>LINARES</t>
   </si>
   <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>FERRAL</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
   </si>
   <si>
     <t>CUAHUA</t>
@@ -196,55 +265,46 @@
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>FERRAL</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>CORDOBA</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>KARLA IRAN</t>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>KARLA MICHEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>BRENDA ELENA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>ALMA LIZETH</t>
   </si>
   <si>
     <t>GERARDO RAUL</t>
@@ -253,97 +313,82 @@
     <t>MARTIN</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ELISA</t>
   </si>
   <si>
     <t>EDITH</t>
   </si>
   <si>
+    <t>JHOVANA</t>
+  </si>
+  <si>
     <t>ANDRES</t>
   </si>
   <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
+    <t>AZAEL</t>
+  </si>
+  <si>
+    <t>ALLISSON NICOLE</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ROSA JATZIRI</t>
+  </si>
+  <si>
+    <t>VALERIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>CECILIA ARLETH</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
   </si>
   <si>
     <t>PERLA</t>
   </si>
   <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
     <t>ERICA</t>
   </si>
   <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
     <t>JAVIER FERNANDO</t>
   </si>
   <si>
     <t>ALEXIS</t>
   </si>
   <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>JHOVANA</t>
-  </si>
-  <si>
-    <t>AZAEL</t>
-  </si>
-  <si>
-    <t>ALLISSON NICOLE</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ROSA JATZIRI</t>
-  </si>
-  <si>
-    <t>VALERIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>CECILIA ARLETH</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
+    <t>AIDA</t>
   </si>
   <si>
     <t>EDUARDO ULISES</t>
@@ -1196,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1228,16 +1273,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920042</v>
+        <v>19330051920045</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1246,21 +1291,21 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920055</v>
+        <v>19330051920081</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1269,159 +1314,159 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920056</v>
+        <v>19330051920284</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920081</v>
+        <v>19330051920289</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920242</v>
+        <v>19330051920323</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920278</v>
+        <v>19330051920352</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920284</v>
+        <v>19330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920286</v>
+        <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920377</v>
+        <v>18330051920188</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1430,21 +1475,21 @@
         <v>13</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920256</v>
+        <v>19330051920251</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1453,21 +1498,21 @@
         <v>14</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920258</v>
+        <v>19330051920400</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1476,67 +1521,67 @@
         <v>14</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920257</v>
+        <v>19330051920046</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920407</v>
+        <v>19330051920055</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920046</v>
+        <v>19330051920056</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1545,7 +1590,7 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1553,13 +1598,13 @@
         <v>18330051920022</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1568,7 +1613,7 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1576,13 +1621,13 @@
         <v>19330051920074</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1591,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1599,13 +1644,13 @@
         <v>19330051920269</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1614,21 +1659,21 @@
         <v>11</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>18330051920321</v>
+        <v>18330051920242</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1637,21 +1682,21 @@
         <v>11</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920449</v>
+        <v>18330051920321</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1660,21 +1705,21 @@
         <v>11</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920343</v>
+        <v>19330051920278</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1683,21 +1728,21 @@
         <v>11</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920292</v>
+        <v>19330051920449</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1706,21 +1751,21 @@
         <v>11</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920293</v>
+        <v>19330051920343</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1729,21 +1774,21 @@
         <v>11</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920298</v>
+        <v>19330051920292</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1752,21 +1797,21 @@
         <v>11</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920299</v>
+        <v>19330051920293</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1775,21 +1820,21 @@
         <v>11</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920443</v>
+        <v>19330051920298</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1798,67 +1843,67 @@
         <v>11</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920307</v>
+        <v>19330051920299</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920312</v>
+        <v>19330051920443</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920323</v>
+        <v>19330051920307</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1867,21 +1912,21 @@
         <v>12</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920321</v>
+        <v>19330051920312</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1890,21 +1935,21 @@
         <v>12</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920345</v>
+        <v>19330051920321</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -1913,21 +1958,21 @@
         <v>12</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920350</v>
+        <v>19330051920345</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -1936,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1944,13 +1989,13 @@
         <v>18330051920097</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -1959,21 +2004,21 @@
         <v>13</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>18330051920108</v>
+        <v>19330051920377</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -1987,39 +2032,39 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920250</v>
+        <v>18330051920108</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920254</v>
+        <v>19330051920250</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2028,21 +2073,21 @@
         <v>14</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920403</v>
+        <v>19330051920256</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2051,7 +2096,122 @@
         <v>14</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>19330051920254</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>19330051920258</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>19330051920257</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" t="s">
+        <v>122</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>19330051920260</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>19330051920403</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="161">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -112,21 +115,30 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MONSALVO</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>COSCAHUA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -142,18 +154,21 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
     <t>SUAREZ</t>
   </si>
   <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -163,30 +178,45 @@
     <t>CARDENAS</t>
   </si>
   <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
     <t>LLAME</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>ROQUE</t>
   </si>
   <si>
@@ -196,9 +226,6 @@
     <t>ALTAMIRANO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>BRUNO</t>
   </si>
   <si>
@@ -208,6 +235,9 @@
     <t>PALMA</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
     <t>QUINTERO</t>
   </si>
   <si>
@@ -220,6 +250,9 @@
     <t>PAZ</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -232,9 +265,15 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>FERRAL</t>
   </si>
   <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
@@ -244,7 +283,7 @@
     <t>AMADOR</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>TZOPITL</t>
   </si>
   <si>
     <t>MENDEZ</t>
@@ -253,6 +292,9 @@
     <t>CORDOBA</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>GUIZA</t>
   </si>
   <si>
@@ -265,18 +307,33 @@
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>EUSEBIO</t>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
   </si>
   <si>
     <t>MONSERRAT</t>
   </si>
   <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
     <t>CONCEPCION</t>
   </si>
   <si>
@@ -301,9 +358,15 @@
     <t>VALERIA</t>
   </si>
   <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
     <t>ANGEL GERARDO</t>
   </si>
   <si>
+    <t>CARLOS ADRIAN</t>
+  </si>
+  <si>
     <t>ALMA LIZETH</t>
   </si>
   <si>
@@ -316,6 +379,12 @@
     <t>ISAAC ALESSANDRO</t>
   </si>
   <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
     <t>IVAN</t>
   </si>
   <si>
@@ -343,12 +412,18 @@
     <t>ROSA JATZIRI</t>
   </si>
   <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
     <t>VALERIA GUADALUPE</t>
   </si>
   <si>
     <t>CECILIA ARLETH</t>
   </si>
   <si>
+    <t>LAISHA STEFANY</t>
+  </si>
+  <si>
     <t>ASHLEY ZURELY</t>
   </si>
   <si>
@@ -358,21 +433,42 @@
     <t>KEVIN HONAM</t>
   </si>
   <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
     <t>GWINETH</t>
   </si>
   <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
     <t>HILARIO</t>
   </si>
   <si>
     <t>PERLA</t>
   </si>
   <si>
+    <t>DARIANA MONSERRAT</t>
+  </si>
+  <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
     <t>ANGELA ALESSANDRA</t>
   </si>
   <si>
@@ -388,10 +484,22 @@
     <t>ALEXIS</t>
   </si>
   <si>
+    <t>WENDY</t>
+  </si>
+  <si>
     <t>AIDA</t>
   </si>
   <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
     <t>EDUARDO ULISES</t>
+  </si>
+  <si>
+    <t>CESAR JOVANI</t>
   </si>
 </sst>
 </file>
@@ -792,10 +900,10 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>8</v>
@@ -804,7 +912,7 @@
         <v>34.78</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -818,10 +926,10 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -844,10 +952,10 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>16</v>
@@ -856,7 +964,7 @@
         <v>42.11</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -870,10 +978,10 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>23</v>
@@ -882,7 +990,7 @@
         <v>62.16</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -896,10 +1004,10 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -908,7 +1016,7 @@
         <v>39.39</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -961,16 +1069,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>16</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>30.43</v>
+      </c>
+      <c r="H2">
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -984,16 +1095,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>38.71</v>
+      </c>
+      <c r="H3">
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1007,16 +1121,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>31.58</v>
+      </c>
+      <c r="H4">
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1030,16 +1147,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>56.76</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1053,16 +1173,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>21.21</v>
+      </c>
+      <c r="H6">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -1115,19 +1238,19 @@
         <v>23</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
+      </c>
+      <c r="F2">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
       <c r="G2">
-        <v>34.78</v>
+        <v>30.43</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1141,16 +1264,16 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>48.39</v>
+        <v>38.71</v>
       </c>
       <c r="H3">
         <v>6.2</v>
@@ -1167,19 +1290,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>31.58</v>
+      </c>
+      <c r="H4">
         <v>6</v>
-      </c>
-      <c r="F4">
-        <v>16</v>
-      </c>
-      <c r="G4">
-        <v>42.11</v>
-      </c>
-      <c r="H4">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1193,19 +1316,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>62.16</v>
+        <v>56.76</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1219,19 +1342,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E6">
+        <v>26</v>
+      </c>
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
       <c r="G6">
-        <v>39.39</v>
+        <v>21.21</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1273,16 +1396,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>18330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1291,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1302,10 +1425,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1314,21 +1437,21 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920284</v>
+        <v>19330051920273</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1342,16 +1465,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920289</v>
+        <v>19330051920284</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1360,44 +1483,44 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920323</v>
+        <v>19330051920289</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920352</v>
+        <v>19330051920323</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1411,39 +1534,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920366</v>
+        <v>19330051920352</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920436</v>
+        <v>19330051920366</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1452,21 +1575,21 @@
         <v>13</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>18330051920188</v>
+        <v>19330051920436</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1475,44 +1598,44 @@
         <v>13</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920251</v>
+        <v>18330051920188</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920400</v>
+        <v>19330051920251</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1526,62 +1649,62 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920046</v>
+        <v>19330051920433</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920055</v>
+        <v>19330051920400</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920056</v>
+        <v>18330051920009</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1590,21 +1713,21 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920022</v>
+        <v>19330051920046</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1613,21 +1736,21 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920074</v>
+        <v>19330051920055</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1636,50 +1759,50 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920269</v>
+        <v>19330051920056</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>18330051920242</v>
+        <v>18330051920022</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1687,45 +1810,45 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>18330051920321</v>
+        <v>19330051920059</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920278</v>
+        <v>19330051920068</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1733,39 +1856,39 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920449</v>
+        <v>19330051920074</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920343</v>
+        <v>19330051920269</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1779,16 +1902,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920292</v>
+        <v>18330051920242</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1797,21 +1920,21 @@
         <v>11</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920293</v>
+        <v>18330051920321</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1825,16 +1948,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920298</v>
+        <v>19330051920278</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1848,16 +1971,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920299</v>
+        <v>19330051920449</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1871,16 +1994,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920443</v>
+        <v>19330051920343</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1894,206 +2017,206 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920307</v>
+        <v>19330051920292</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920312</v>
+        <v>19330051920293</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920321</v>
+        <v>19330051920295</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920345</v>
+        <v>19330051920298</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>18330051920097</v>
+        <v>19330051920299</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920377</v>
+        <v>19330051920301</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>18330051920108</v>
+        <v>19330051920443</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920250</v>
+        <v>19330051920307</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920256</v>
+        <v>19330051920312</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2101,117 +2224,531 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920254</v>
+        <v>19330051920316</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920258</v>
+        <v>19330051920321</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920257</v>
+        <v>19330051920330</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920260</v>
+        <v>19330051920337</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
+        <v>19330051920345</v>
+      </c>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>19330051920351</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>18330051920097</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>19330051920377</v>
+      </c>
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>19330051920378</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>18330051920108</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>19330051920369</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>19330051920248</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>19330051920250</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" t="s">
+        <v>150</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>19330051920256</v>
+      </c>
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" t="s">
+        <v>151</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>19330051920254</v>
+      </c>
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>19330051920258</v>
+      </c>
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>19330051920257</v>
+      </c>
+      <c r="B54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" t="s">
+        <v>95</v>
+      </c>
+      <c r="D54" t="s">
+        <v>154</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>19330051920255</v>
+      </c>
+      <c r="B55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D55" t="s">
+        <v>155</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>19330051920260</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" t="s">
+        <v>156</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>19330051920263</v>
+      </c>
+      <c r="B57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" t="s">
+        <v>157</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>19330051920402</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
         <v>19330051920403</v>
       </c>
-      <c r="B42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
         <v>14</v>
       </c>
-      <c r="G42">
-        <v>3</v>
+      <c r="G59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>19330051920405</v>
+      </c>
+      <c r="B60" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" t="s">
+        <v>101</v>
+      </c>
+      <c r="D60" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="159">
   <si>
     <t>Mat</t>
   </si>
@@ -103,12 +103,15 @@
     <t>VILLA</t>
   </si>
   <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>VALDES</t>
   </si>
   <si>
@@ -193,9 +196,6 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -205,9 +205,6 @@
     <t>LLAME</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
@@ -226,7 +223,10 @@
     <t>ALTAMIRANO</t>
   </si>
   <si>
-    <t>BRUNO</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>MARIN</t>
@@ -253,9 +253,6 @@
     <t>PACHECO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
@@ -292,9 +289,6 @@
     <t>CORDOBA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>GUIZA</t>
   </si>
   <si>
@@ -346,12 +340,15 @@
     <t>ADAN</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>ASTRID</t>
   </si>
   <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
     <t>BRENDA ELENA</t>
   </si>
   <si>
@@ -461,9 +458,6 @@
   </si>
   <si>
     <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
   </si>
   <si>
     <t>BRANDON AXEL</t>
@@ -1402,10 +1396,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1425,10 +1419,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1448,10 +1442,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1460,7 +1454,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1471,10 +1465,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1483,7 +1477,7 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1494,10 +1488,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1506,7 +1500,7 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1517,10 +1511,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1540,10 +1534,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1557,16 +1551,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920366</v>
+        <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1575,21 +1569,21 @@
         <v>13</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920436</v>
+        <v>19330051920393</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1603,16 +1597,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920188</v>
+        <v>19330051920369</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1626,39 +1620,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920251</v>
+        <v>18330051920188</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920433</v>
+        <v>19330051920251</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1667,21 +1661,21 @@
         <v>14</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920400</v>
+        <v>19330051920433</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1690,44 +1684,44 @@
         <v>14</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>18330051920009</v>
+        <v>19330051920400</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920046</v>
+        <v>18330051920009</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1741,16 +1735,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920055</v>
+        <v>19330051920046</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1764,16 +1758,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920056</v>
+        <v>19330051920055</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1787,16 +1781,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>18330051920022</v>
+        <v>19330051920056</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1805,21 +1799,21 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920059</v>
+        <v>18330051920022</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1828,21 +1822,21 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920068</v>
+        <v>19330051920059</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1851,21 +1845,21 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920074</v>
+        <v>19330051920068</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1874,44 +1868,44 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920269</v>
+        <v>19330051920074</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>18330051920242</v>
+        <v>19330051920269</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1920,21 +1914,21 @@
         <v>11</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>18330051920321</v>
+        <v>18330051920242</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1943,21 +1937,21 @@
         <v>11</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920278</v>
+        <v>18330051920321</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1971,16 +1965,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920449</v>
+        <v>19330051920278</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1989,21 +1983,21 @@
         <v>11</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920343</v>
+        <v>19330051920449</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2012,21 +2006,21 @@
         <v>11</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920292</v>
+        <v>19330051920343</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2035,21 +2029,21 @@
         <v>11</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920293</v>
+        <v>19330051920292</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2058,21 +2052,21 @@
         <v>11</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920295</v>
+        <v>19330051920293</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2086,16 +2080,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920298</v>
+        <v>19330051920295</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2104,21 +2098,21 @@
         <v>11</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920299</v>
+        <v>19330051920298</v>
       </c>
       <c r="B33" t="s">
         <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2127,21 +2121,21 @@
         <v>11</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920301</v>
+        <v>19330051920299</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2150,21 +2144,21 @@
         <v>11</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920443</v>
+        <v>19330051920301</v>
       </c>
       <c r="B35" t="s">
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2173,27 +2167,27 @@
         <v>11</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920307</v>
+        <v>19330051920443</v>
       </c>
       <c r="B36" t="s">
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2201,16 +2195,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920312</v>
+        <v>19330051920307</v>
       </c>
       <c r="B37" t="s">
         <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2219,21 +2213,21 @@
         <v>12</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920316</v>
+        <v>19330051920312</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2242,21 +2236,21 @@
         <v>12</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920321</v>
+        <v>19330051920316</v>
       </c>
       <c r="B39" t="s">
         <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2270,16 +2264,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920330</v>
+        <v>19330051920321</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2293,16 +2287,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920337</v>
+        <v>19330051920330</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2316,16 +2310,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920345</v>
+        <v>19330051920337</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2339,16 +2333,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920351</v>
+        <v>19330051920345</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2362,39 +2356,39 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>18330051920097</v>
+        <v>19330051920351</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>19330051920377</v>
+        <v>18330051920097</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -2403,21 +2397,21 @@
         <v>13</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>19330051920378</v>
+        <v>19330051920377</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
@@ -2426,21 +2420,21 @@
         <v>13</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>18330051920108</v>
+        <v>19330051920378</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -2454,16 +2448,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>19330051920369</v>
+        <v>18330051920108</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
@@ -2472,7 +2466,7 @@
         <v>13</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2483,10 +2477,10 @@
         <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2506,10 +2500,10 @@
         <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2526,13 +2520,13 @@
         <v>19330051920256</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2549,13 +2543,13 @@
         <v>19330051920254</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2572,13 +2566,13 @@
         <v>19330051920258</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2595,13 +2589,13 @@
         <v>19330051920257</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D54" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2618,13 +2612,13 @@
         <v>19330051920255</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2644,10 +2638,10 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2664,13 +2658,13 @@
         <v>19330051920263</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C57" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2690,10 +2684,10 @@
         <v>25</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D58" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2710,13 +2704,13 @@
         <v>19330051920403</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D59" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2733,13 +2727,13 @@
         <v>19330051920405</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="135">
   <si>
     <t>Mat</t>
   </si>
@@ -82,136 +82,160 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>VALDES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>PAZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>LINARES</t>
   </si>
   <si>
     <t>ROQUE</t>
@@ -220,112 +244,112 @@
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>ALTAMIRANO</t>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>VERA</t>
   </si>
   <si>
     <t>QUINTERO</t>
   </si>
   <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>FERRAL</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>CORDOBA</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
     <t>BONILLA</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>JOSUE YAMIN</t>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>MARTI NEFTALI</t>
   </si>
   <si>
     <t>MONSERRAT</t>
   </si>
   <si>
-    <t>ESDRAS ALAN</t>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>BRENDA ELENA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>CARLOS ADRIAN</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>JHOVANA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
   </si>
   <si>
     <t>CONCEPCION</t>
@@ -334,166 +358,70 @@
     <t>KARLA MICHEL</t>
   </si>
   <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>BRENDA ELENA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ROSA JATZIRI</t>
+  </si>
+  <si>
+    <t>CECILIA ARLETH</t>
+  </si>
+  <si>
+    <t>LAISHA STEFANY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>WENDY</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
   </si>
   <si>
     <t>ANGEL GERARDO</t>
   </si>
   <si>
-    <t>CARLOS ADRIAN</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>JHOVANA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>AZAEL</t>
-  </si>
-  <si>
-    <t>ALLISSON NICOLE</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ROSA JATZIRI</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>VALERIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>CECILIA ARLETH</t>
-  </si>
-  <si>
-    <t>LAISHA STEFANY</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ERICA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
     <t>EDUARDO ULISES</t>
   </si>
   <si>
     <t>CESAR JOVANI</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
   </si>
 </sst>
 </file>
@@ -1235,13 +1163,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>30.43</v>
+        <v>47.83</v>
       </c>
       <c r="H2">
         <v>5.6</v>
@@ -1261,16 +1189,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>38.71</v>
+        <v>54.84</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1287,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>31.58</v>
+        <v>44.74</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1313,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>56.76</v>
+        <v>72.97</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1339,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>21.21</v>
+        <v>24.24</v>
       </c>
       <c r="H6">
         <v>5.5</v>
@@ -1358,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1390,16 +1318,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920078</v>
+        <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1408,21 +1336,21 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920081</v>
+        <v>19330051920418</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1431,44 +1359,44 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920273</v>
+        <v>19330051920081</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920284</v>
+        <v>19330051920286</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1477,21 +1405,21 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920289</v>
+        <v>19330051920443</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1511,10 +1439,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1528,7 +1456,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920352</v>
+        <v>19330051920360</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1537,13 +1465,13 @@
         <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1551,16 +1479,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920436</v>
+        <v>18330051920188</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1574,45 +1502,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920393</v>
+        <v>19330051920251</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920369</v>
+        <v>19330051920259</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1620,108 +1548,108 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920188</v>
+        <v>18330051920009</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920251</v>
+        <v>19330051920045</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920433</v>
+        <v>19330051920049</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920400</v>
+        <v>18330051920022</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920009</v>
+        <v>19330051920058</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1735,16 +1663,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920046</v>
+        <v>19330051920050</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1758,22 +1686,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920055</v>
+        <v>19330051920269</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1781,22 +1709,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920056</v>
+        <v>18330051920242</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1804,45 +1732,45 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>18330051920022</v>
+        <v>18330051920321</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920059</v>
+        <v>19330051920278</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1850,62 +1778,62 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920068</v>
+        <v>19330051920284</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920074</v>
+        <v>19330051920289</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920269</v>
+        <v>19330051920292</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1919,16 +1847,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>18330051920242</v>
+        <v>19330051920293</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1942,16 +1870,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>18330051920321</v>
+        <v>19330051920299</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1960,21 +1888,21 @@
         <v>11</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920278</v>
+        <v>19330051920301</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1988,22 +1916,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920449</v>
+        <v>19330051920307</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2011,22 +1939,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920343</v>
+        <v>19330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2034,68 +1962,68 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920292</v>
+        <v>19330051920321</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920293</v>
+        <v>19330051920338</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920295</v>
+        <v>19330051920351</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2103,22 +2031,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920298</v>
+        <v>18330051920108</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2126,22 +2054,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920299</v>
+        <v>19330051920248</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2149,22 +2077,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920301</v>
+        <v>19330051920250</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2172,22 +2100,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920443</v>
+        <v>19330051920254</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2195,22 +2123,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920307</v>
+        <v>19330051920258</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2218,45 +2146,45 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920312</v>
+        <v>19330051920257</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920316</v>
+        <v>19330051920255</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2264,22 +2192,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920321</v>
+        <v>19330051920260</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2287,22 +2215,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920330</v>
+        <v>19330051920263</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="D41" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2310,22 +2238,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920337</v>
+        <v>19330051920400</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2333,22 +2261,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920345</v>
+        <v>19330051920403</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2356,22 +2284,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>19330051920351</v>
+        <v>19330051920405</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2379,369 +2307,24 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>18330051920097</v>
+        <v>19330051920414</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>19330051920377</v>
-      </c>
-      <c r="B46" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" t="s">
-        <v>144</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>19330051920378</v>
-      </c>
-      <c r="B47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" t="s">
-        <v>145</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>18330051920108</v>
-      </c>
-      <c r="B48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48" t="s">
-        <v>146</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>19330051920248</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>37</v>
-      </c>
-      <c r="D49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>19330051920250</v>
-      </c>
-      <c r="B50" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" t="s">
-        <v>148</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>19330051920256</v>
-      </c>
-      <c r="B51" t="s">
-        <v>39</v>
-      </c>
-      <c r="C51" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" t="s">
-        <v>149</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>19330051920254</v>
-      </c>
-      <c r="B52" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" t="s">
-        <v>150</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>14</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>19330051920258</v>
-      </c>
-      <c r="B53" t="s">
-        <v>39</v>
-      </c>
-      <c r="C53" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" t="s">
-        <v>151</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>19330051920257</v>
-      </c>
-      <c r="B54" t="s">
-        <v>39</v>
-      </c>
-      <c r="C54" t="s">
-        <v>93</v>
-      </c>
-      <c r="D54" t="s">
-        <v>152</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>19330051920255</v>
-      </c>
-      <c r="B55" t="s">
-        <v>39</v>
-      </c>
-      <c r="C55" t="s">
-        <v>94</v>
-      </c>
-      <c r="D55" t="s">
-        <v>153</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>19330051920260</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" t="s">
-        <v>154</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>19330051920263</v>
-      </c>
-      <c r="B57" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" t="s">
-        <v>96</v>
-      </c>
-      <c r="D57" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>19330051920402</v>
-      </c>
-      <c r="B58" t="s">
-        <v>25</v>
-      </c>
-      <c r="C58" t="s">
-        <v>97</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>19330051920403</v>
-      </c>
-      <c r="B59" t="s">
-        <v>45</v>
-      </c>
-      <c r="C59" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" t="s">
-        <v>157</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>19330051920405</v>
-      </c>
-      <c r="B60" t="s">
-        <v>29</v>
-      </c>
-      <c r="C60" t="s">
-        <v>99</v>
-      </c>
-      <c r="D60" t="s">
-        <v>158</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="137">
   <si>
     <t>Mat</t>
   </si>
@@ -103,6 +103,9 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>VALDES</t>
   </si>
   <si>
@@ -311,6 +314,9 @@
   </si>
   <si>
     <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
   </si>
   <si>
     <t>BRENDA ELENA</t>
@@ -1286,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1324,10 +1330,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1347,10 +1353,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1370,10 +1376,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1393,10 +1399,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1416,10 +1422,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1439,10 +1445,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1462,10 +1468,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1479,16 +1485,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>18330051920188</v>
+        <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1502,7 +1508,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920251</v>
+        <v>18330051920188</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1511,13 +1517,13 @@
         <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1525,7 +1531,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920259</v>
+        <v>19330051920251</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -1534,7 +1540,7 @@
         <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1548,39 +1554,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920009</v>
+        <v>19330051920259</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920045</v>
+        <v>18330051920009</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1594,16 +1600,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920049</v>
+        <v>19330051920045</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1617,16 +1623,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>18330051920022</v>
+        <v>19330051920049</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1640,16 +1646,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920058</v>
+        <v>18330051920022</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1663,16 +1669,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920050</v>
+        <v>19330051920058</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1686,22 +1692,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920269</v>
+        <v>19330051920050</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1709,7 +1715,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>18330051920242</v>
+        <v>19330051920269</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -1718,7 +1724,7 @@
         <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1732,16 +1738,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>18330051920321</v>
+        <v>18330051920242</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1755,16 +1761,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920278</v>
+        <v>18330051920321</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1778,7 +1784,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920284</v>
+        <v>19330051920278</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
@@ -1787,7 +1793,7 @@
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1801,7 +1807,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920289</v>
+        <v>19330051920284</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1810,7 +1816,7 @@
         <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1824,16 +1830,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920292</v>
+        <v>19330051920289</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1847,16 +1853,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920293</v>
+        <v>19330051920292</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1870,16 +1876,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920299</v>
+        <v>19330051920293</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1893,7 +1899,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920301</v>
+        <v>19330051920299</v>
       </c>
       <c r="B27" t="s">
         <v>45</v>
@@ -1902,7 +1908,7 @@
         <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1916,7 +1922,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920307</v>
+        <v>19330051920301</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -1925,13 +1931,13 @@
         <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1939,7 +1945,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920312</v>
+        <v>19330051920307</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -1948,7 +1954,7 @@
         <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1962,16 +1968,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920321</v>
+        <v>19330051920312</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
         <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1985,16 +1991,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920338</v>
+        <v>19330051920321</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
         <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2008,16 +2014,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920351</v>
+        <v>19330051920338</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2031,22 +2037,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>18330051920108</v>
+        <v>19330051920351</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2054,22 +2060,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920248</v>
+        <v>18330051920108</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2077,16 +2083,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920250</v>
+        <v>19330051920248</v>
       </c>
       <c r="B35" t="s">
         <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2100,16 +2106,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920254</v>
+        <v>19330051920250</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2123,16 +2129,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920258</v>
+        <v>19330051920254</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2146,16 +2152,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920257</v>
+        <v>19330051920258</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
         <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2169,16 +2175,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920255</v>
+        <v>19330051920257</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
         <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2192,16 +2198,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920260</v>
+        <v>19330051920255</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
         <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2215,16 +2221,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920263</v>
+        <v>19330051920260</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2238,16 +2244,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920400</v>
+        <v>19330051920263</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2261,7 +2267,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920403</v>
+        <v>19330051920400</v>
       </c>
       <c r="B43" t="s">
         <v>55</v>
@@ -2270,7 +2276,7 @@
         <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2284,7 +2290,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>19330051920405</v>
+        <v>19330051920403</v>
       </c>
       <c r="B44" t="s">
         <v>56</v>
@@ -2293,7 +2299,7 @@
         <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2307,7 +2313,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>19330051920414</v>
+        <v>19330051920405</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
@@ -2316,7 +2322,7 @@
         <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2325,6 +2331,29 @@
         <v>14</v>
       </c>
       <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>19330051920414</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46">
         <v>1</v>
       </c>
     </row>
